--- a/directorio_osc2026.xlsx
+++ b/directorio_osc2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gil\Pictures\Osc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{781FE811-0203-4502-B3E4-13C83765C4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE83E0CE-2EF8-4ADA-928A-CBCABE1557A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27C9B065-C151-427A-84BF-57BA45A87D76}"/>
+    <workbookView xWindow="690" yWindow="690" windowWidth="7500" windowHeight="6000" xr2:uid="{27C9B065-C151-427A-84BF-57BA45A87D76}"/>
   </bookViews>
   <sheets>
     <sheet name="directorio_osc" sheetId="1" r:id="rId1"/>
